--- a/artfynd/A 43719-2025 artfynd.xlsx
+++ b/artfynd/A 43719-2025 artfynd.xlsx
@@ -923,7 +923,7 @@
         <v>136482365</v>
       </c>
       <c r="B4" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
         <v>136482366</v>
       </c>
       <c r="B5" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1234,7 +1234,7 @@
         <v>136482353</v>
       </c>
       <c r="B7" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1341,7 +1341,7 @@
         <v>136482354</v>
       </c>
       <c r="B8" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 43719-2025 artfynd.xlsx
+++ b/artfynd/A 43719-2025 artfynd.xlsx
@@ -923,7 +923,7 @@
         <v>136482365</v>
       </c>
       <c r="B4" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
         <v>136482366</v>
       </c>
       <c r="B5" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 43719-2025 artfynd.xlsx
+++ b/artfynd/A 43719-2025 artfynd.xlsx
@@ -923,7 +923,7 @@
         <v>136482365</v>
       </c>
       <c r="B4" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
         <v>136482366</v>
       </c>
       <c r="B5" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 43719-2025 artfynd.xlsx
+++ b/artfynd/A 43719-2025 artfynd.xlsx
@@ -923,7 +923,7 @@
         <v>136482365</v>
       </c>
       <c r="B4" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
         <v>136482366</v>
       </c>
       <c r="B5" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 43719-2025 artfynd.xlsx
+++ b/artfynd/A 43719-2025 artfynd.xlsx
@@ -923,7 +923,7 @@
         <v>136482365</v>
       </c>
       <c r="B4" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
         <v>136482366</v>
       </c>
       <c r="B5" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 43719-2025 artfynd.xlsx
+++ b/artfynd/A 43719-2025 artfynd.xlsx
@@ -923,7 +923,7 @@
         <v>136482365</v>
       </c>
       <c r="B4" t="n">
-        <v>79485</v>
+        <v>79535</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
         <v>136482366</v>
       </c>
       <c r="B5" t="n">
-        <v>79485</v>
+        <v>79535</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1234,7 +1234,7 @@
         <v>136482353</v>
       </c>
       <c r="B7" t="n">
-        <v>58008</v>
+        <v>58035</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1341,7 +1341,7 @@
         <v>136482354</v>
       </c>
       <c r="B8" t="n">
-        <v>58008</v>
+        <v>58035</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 43719-2025 artfynd.xlsx
+++ b/artfynd/A 43719-2025 artfynd.xlsx
@@ -923,7 +923,7 @@
         <v>136482365</v>
       </c>
       <c r="B4" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
         <v>136482366</v>
       </c>
       <c r="B5" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1234,7 +1234,7 @@
         <v>136482353</v>
       </c>
       <c r="B7" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1341,7 +1341,7 @@
         <v>136482354</v>
       </c>
       <c r="B8" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
